--- a/data/trans_orig/P34-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2007</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62210</t>
+          <t>61782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97551</t>
+          <t>96664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42526</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71263</t>
+          <t>73489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113793</t>
+          <t>114895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158210</t>
+          <t>159590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105070</t>
+          <t>102469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146024</t>
+          <t>144012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46753</t>
+          <t>47894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75058</t>
+          <t>78299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159995</t>
+          <t>157711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210913</t>
+          <t>211324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>407957</t>
+          <t>405555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>475497</t>
+          <t>469667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>747695</t>
+          <t>746230</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>817190</t>
+          <t>814795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1178405</t>
+          <t>1176166</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1271892</t>
+          <t>1271143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>343711</t>
+          <t>345093</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>406441</t>
+          <t>406059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370803</t>
+          <t>373481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>434484</t>
+          <t>442239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>735684</t>
+          <t>739354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>824226</t>
+          <t>827181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>129805</t>
+          <t>129508</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176675</t>
+          <t>176871</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52501</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84022</t>
+          <t>83731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190627</t>
+          <t>191324</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>247248</t>
+          <t>248807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>310533</t>
+          <t>310685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>374601</t>
+          <t>377591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126554</t>
+          <t>125866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172356</t>
+          <t>175121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>450083</t>
+          <t>454144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>534767</t>
+          <t>533359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545975</t>
+          <t>546002</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623781</t>
+          <t>623400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>904008</t>
+          <t>904175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>980684</t>
+          <t>980552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1468735</t>
+          <t>1471184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1582274</t>
+          <t>1584051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>564320</t>
+          <t>560842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>642651</t>
+          <t>638469</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>383109</t>
+          <t>385650</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>454117</t>
+          <t>456040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>962770</t>
+          <t>968157</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1067941</t>
+          <t>1070047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38503</t>
+          <t>36816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40305</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69253</t>
+          <t>68199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58025</t>
+          <t>57453</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>92735</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>177636</t>
+          <t>178238</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>223936</t>
+          <t>224404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192871</t>
+          <t>193217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>237653</t>
+          <t>237450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379877</t>
+          <t>384059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>442291</t>
+          <t>446164</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258696</t>
+          <t>258404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305485</t>
+          <t>305317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205797</t>
+          <t>204821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>249585</t>
+          <t>250134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>476658</t>
+          <t>476140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>541936</t>
+          <t>539255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214810</t>
+          <t>214756</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>274674</t>
+          <t>273749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115127</t>
+          <t>114506</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160534</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>343805</t>
+          <t>341636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>418013</t>
+          <t>418479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>481763</t>
+          <t>476282</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>565719</t>
+          <t>564738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201678</t>
+          <t>199384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261238</t>
+          <t>259002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>698424</t>
+          <t>697578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>804788</t>
+          <t>801972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1161728</t>
+          <t>1168790</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1276831</t>
+          <t>1278503</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1875465</t>
+          <t>1885510</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1994159</t>
+          <t>1994784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3076240</t>
+          <t>3082529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3244088</t>
+          <t>3239080</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1202725</t>
+          <t>1199176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1310781</t>
+          <t>1310897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>997222</t>
+          <t>991252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1111501</t>
+          <t>1099024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2236976</t>
+          <t>2229526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2389398</t>
+          <t>2384239</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2012</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2012 (tasa de respuesta: 99,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>91097</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131603</t>
+          <t>131223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83572</t>
+          <t>87159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126977</t>
+          <t>124859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186226</t>
+          <t>186597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246855</t>
+          <t>247822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>464549</t>
+          <t>466152</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>530671</t>
+          <t>533940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>712916</t>
+          <t>711819</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>782786</t>
+          <t>784420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1197039</t>
+          <t>1193464</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1296694</t>
+          <t>1293216</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>307479</t>
+          <t>306313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>369616</t>
+          <t>368995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>438581</t>
+          <t>436020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>506639</t>
+          <t>507948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>754606</t>
+          <t>764831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>853933</t>
+          <t>857150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>85803</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124524</t>
+          <t>125995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>96493</t>
+          <t>95664</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138779</t>
+          <t>136753</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>274887</t>
+          <t>275897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>337489</t>
+          <t>343172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164965</t>
+          <t>168334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219082</t>
+          <t>223839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>457103</t>
+          <t>452769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>542743</t>
+          <t>541318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>944909</t>
+          <t>944759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1034711</t>
+          <t>1033744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1092859</t>
+          <t>1093379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1178191</t>
+          <t>1177815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2059774</t>
+          <t>2058590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2184161</t>
+          <t>2178807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>511502</t>
+          <t>508999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>591145</t>
+          <t>593608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>371120</t>
+          <t>372530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>444325</t>
+          <t>445996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>899048</t>
+          <t>904842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1012142</t>
+          <t>1012203</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>32554</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59241</t>
+          <t>60033</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21834</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>45166</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60654</t>
+          <t>60916</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>98150</t>
+          <t>98015</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>213094</t>
+          <t>211207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>259924</t>
+          <t>258744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238675</t>
+          <t>236166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283113</t>
+          <t>282725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>464026</t>
+          <t>466014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>527948</t>
+          <t>528903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164503</t>
+          <t>165169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210935</t>
+          <t>210631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135715</t>
+          <t>134349</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176258</t>
+          <t>176507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>313224</t>
+          <t>308724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373578</t>
+          <t>372240</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115268</t>
+          <t>116031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>161112</t>
+          <t>163832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>35297</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137911</t>
+          <t>138334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189319</t>
+          <t>190911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>421585</t>
+          <t>422698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>502941</t>
+          <t>504574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294103</t>
+          <t>293677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>363818</t>
+          <t>367848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>729421</t>
+          <t>731475</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>847848</t>
+          <t>842050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1666352</t>
+          <t>1662576</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1788727</t>
+          <t>1776624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2084663</t>
+          <t>2081440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2202796</t>
+          <t>2204343</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3787256</t>
+          <t>3775298</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3952813</t>
+          <t>3949811</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1019337</t>
+          <t>1021059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1129784</t>
+          <t>1129487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>976525</t>
+          <t>978335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1091790</t>
+          <t>1089717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2027212</t>
+          <t>2033737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2186185</t>
+          <t>2188898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2016</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2016 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60597</t>
+          <t>59533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93631</t>
+          <t>92874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>32516</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58466</t>
+          <t>58333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100530</t>
+          <t>99684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142520</t>
+          <t>141925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>295256</t>
+          <t>297911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>347793</t>
+          <t>350120</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>491137</t>
+          <t>486584</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>552946</t>
+          <t>553531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>802849</t>
+          <t>803018</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>886405</t>
+          <t>884350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>314066</t>
+          <t>311842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366026</t>
+          <t>367815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>388541</t>
+          <t>388818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>451742</t>
+          <t>451081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>720266</t>
+          <t>720959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>803998</t>
+          <t>807720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88793</t>
+          <t>88410</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67140</t>
+          <t>65601</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103831</t>
+          <t>103217</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239575</t>
+          <t>239093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304313</t>
+          <t>301238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148153</t>
+          <t>151739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198405</t>
+          <t>201868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>407419</t>
+          <t>408165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487248</t>
+          <t>487333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1037235</t>
+          <t>1031363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1123769</t>
+          <t>1122873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1258664</t>
+          <t>1256452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1342826</t>
+          <t>1340831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2321095</t>
+          <t>2316805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2441355</t>
+          <t>2439168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>596768</t>
+          <t>598069</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>681197</t>
+          <t>687374</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>457395</t>
+          <t>457877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533229</t>
+          <t>533953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1073973</t>
+          <t>1078288</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1193960</t>
+          <t>1194728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17251</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57929</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32472</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57831</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67646</t>
+          <t>67317</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>105810</t>
+          <t>104691</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217667</t>
+          <t>216438</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>264498</t>
+          <t>262708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290630</t>
+          <t>289473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338001</t>
+          <t>335121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>518945</t>
+          <t>520713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>587586</t>
+          <t>590491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>227710</t>
+          <t>228124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>275526</t>
+          <t>273666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165076</t>
+          <t>165162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210281</t>
+          <t>209054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405901</t>
+          <t>398880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>470029</t>
+          <t>469939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72410</t>
+          <t>73470</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112730</t>
+          <t>111710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27177</t>
+          <t>27333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88361</t>
+          <t>88581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130722</t>
+          <t>130784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353946</t>
+          <t>353896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>429864</t>
+          <t>429018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232932</t>
+          <t>231540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>296912</t>
+          <t>294814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>601123</t>
+          <t>600220</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705813</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1588201</t>
+          <t>1583415</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1698015</t>
+          <t>1699856</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2074376</t>
+          <t>2075319</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2189479</t>
+          <t>2192314</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3702944</t>
+          <t>3691867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3870592</t>
+          <t>3854357</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1175358</t>
+          <t>1171832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1282753</t>
+          <t>1287794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1047054</t>
+          <t>1044424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1158477</t>
+          <t>1158941</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2247957</t>
+          <t>2256395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2406523</t>
+          <t>2417426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2023</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2023 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21360</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41264</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>46979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78772</t>
+          <t>77195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109767</t>
+          <t>109555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>60830</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86662</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145260</t>
+          <t>145587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189265</t>
+          <t>186479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>149395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>189411</t>
+          <t>190149</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>282006</t>
+          <t>281625</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>323227</t>
+          <t>323552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>440700</t>
+          <t>444004</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>502113</t>
+          <t>503488</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>198376</t>
+          <t>200032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>240653</t>
+          <t>242462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>347605</t>
+          <t>347486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>389283</t>
+          <t>390276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>555681</t>
+          <t>557793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>615505</t>
+          <t>617764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124253</t>
+          <t>123289</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211234</t>
+          <t>212849</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>38625</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70421</t>
+          <t>70586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>184771</t>
+          <t>180039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>272533</t>
+          <t>269582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>499909</t>
+          <t>499578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1172251</t>
+          <t>1163902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>346041</t>
+          <t>356435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>633030</t>
+          <t>623197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>908827</t>
+          <t>919955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1771657</t>
+          <t>1696359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529834</t>
+          <t>540593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>870307</t>
+          <t>876710</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1062663</t>
+          <t>1075325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1525075</t>
+          <t>1474381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1670898</t>
+          <t>1703639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2279906</t>
+          <t>2264375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>433014</t>
+          <t>446589</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>724398</t>
+          <t>724252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>353458</t>
+          <t>365818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>575592</t>
+          <t>578213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>898744</t>
+          <t>874792</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1257747</t>
+          <t>1249500</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63196</t>
+          <t>63345</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110234</t>
+          <t>110751</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69337</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99286</t>
+          <t>99975</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142055</t>
+          <t>143166</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>194339</t>
+          <t>200024</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201237</t>
+          <t>198634</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>251720</t>
+          <t>250867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254065</t>
+          <t>254287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297050</t>
+          <t>298958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>467793</t>
+          <t>467510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>537230</t>
+          <t>538438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>295200</t>
+          <t>295894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348664</t>
+          <t>353673</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264200</t>
+          <t>264287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>310212</t>
+          <t>311948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>579155</t>
+          <t>574526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>651114</t>
+          <t>648905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>164746</t>
+          <t>162600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>253419</t>
+          <t>247973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>53779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86093</t>
+          <t>85767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243464</t>
+          <t>245221</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>326720</t>
+          <t>328426</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>665615</t>
+          <t>664397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1447996</t>
+          <t>1463525</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>528524</t>
+          <t>521282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>834316</t>
+          <t>806384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1251998</t>
+          <t>1252773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2320132</t>
+          <t>2203069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>908607</t>
+          <t>888362</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1268430</t>
+          <t>1274333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1645971</t>
+          <t>1645391</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2120778</t>
+          <t>2112852</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2656236</t>
+          <t>2645421</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3297349</t>
+          <t>3333412</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>912690</t>
+          <t>891118</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1282906</t>
+          <t>1280067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>939029</t>
+          <t>953541</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1252955</t>
+          <t>1254395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2020720</t>
+          <t>2017138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2494824</t>
+          <t>2480498</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61782</t>
+          <t>61574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96664</t>
+          <t>98331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73489</t>
+          <t>72933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114895</t>
+          <t>112763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159590</t>
+          <t>158600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102469</t>
+          <t>102866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144012</t>
+          <t>146328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78299</t>
+          <t>76897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157711</t>
+          <t>158747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211324</t>
+          <t>213496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>405555</t>
+          <t>407334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>469667</t>
+          <t>469784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>746230</t>
+          <t>750754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>814795</t>
+          <t>820313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1176166</t>
+          <t>1172537</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1271143</t>
+          <t>1272193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>345093</t>
+          <t>348214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>406059</t>
+          <t>409439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>373481</t>
+          <t>371051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>442239</t>
+          <t>436070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>739354</t>
+          <t>736438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>827181</t>
+          <t>825410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>129508</t>
+          <t>127857</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176871</t>
+          <t>172709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83731</t>
+          <t>83536</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>191324</t>
+          <t>191866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>248807</t>
+          <t>246127</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>310685</t>
+          <t>311254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>377591</t>
+          <t>377293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125866</t>
+          <t>125475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175121</t>
+          <t>172712</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>454144</t>
+          <t>450003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>533359</t>
+          <t>534043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546002</t>
+          <t>548325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623400</t>
+          <t>630721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>904175</t>
+          <t>904202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>980552</t>
+          <t>982625</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1471184</t>
+          <t>1471303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1584051</t>
+          <t>1582056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>560842</t>
+          <t>560100</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>638469</t>
+          <t>638997</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>385650</t>
+          <t>383609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>456040</t>
+          <t>451686</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>968157</t>
+          <t>964117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1070047</t>
+          <t>1073482</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>36691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39505</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68199</t>
+          <t>68544</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>57453</t>
+          <t>58124</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>93243</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178238</t>
+          <t>176698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>224404</t>
+          <t>223958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193217</t>
+          <t>192861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>237450</t>
+          <t>234346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>384059</t>
+          <t>382124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446164</t>
+          <t>447410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258404</t>
+          <t>256351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305317</t>
+          <t>306390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204821</t>
+          <t>206559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250134</t>
+          <t>249388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>476140</t>
+          <t>475635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>539255</t>
+          <t>539257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214756</t>
+          <t>214307</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>273749</t>
+          <t>276947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>114506</t>
+          <t>115655</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>158503</t>
+          <t>161815</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>341636</t>
+          <t>343388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>418479</t>
+          <t>417572</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>476282</t>
+          <t>482245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>564738</t>
+          <t>567273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199384</t>
+          <t>202875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259002</t>
+          <t>260733</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>697578</t>
+          <t>700140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>801972</t>
+          <t>802117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1168790</t>
+          <t>1170336</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1278503</t>
+          <t>1281250</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1885510</t>
+          <t>1884086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1994784</t>
+          <t>1999591</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3082529</t>
+          <t>3081151</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3239080</t>
+          <t>3243731</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1199176</t>
+          <t>1201843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1310897</t>
+          <t>1314838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>991252</t>
+          <t>990333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1099024</t>
+          <t>1100891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2229526</t>
+          <t>2232445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2384239</t>
+          <t>2386107</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>36754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44035</t>
+          <t>45080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91097</t>
+          <t>90795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131223</t>
+          <t>130301</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87159</t>
+          <t>83554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124859</t>
+          <t>126535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186597</t>
+          <t>187139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247822</t>
+          <t>242900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>466152</t>
+          <t>467172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>533940</t>
+          <t>530820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>711819</t>
+          <t>711498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>784420</t>
+          <t>780516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1193464</t>
+          <t>1197364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1293216</t>
+          <t>1294625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,35%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>306313</t>
+          <t>305350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368995</t>
+          <t>368894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>436020</t>
+          <t>440253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>507948</t>
+          <t>509602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>764831</t>
+          <t>757580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>857150</t>
+          <t>853503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85803</t>
+          <t>83909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125995</t>
+          <t>126207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>20143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95664</t>
+          <t>95319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136753</t>
+          <t>138523</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>275897</t>
+          <t>274235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>343172</t>
+          <t>342176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168334</t>
+          <t>168887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223839</t>
+          <t>220153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>452769</t>
+          <t>460128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>541318</t>
+          <t>541936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>944759</t>
+          <t>941800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1033744</t>
+          <t>1035703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1093379</t>
+          <t>1095969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1177815</t>
+          <t>1175149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2058590</t>
+          <t>2061764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2178807</t>
+          <t>2187605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>508999</t>
+          <t>512325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>593608</t>
+          <t>596237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>372530</t>
+          <t>370931</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>445996</t>
+          <t>443690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>904842</t>
+          <t>905284</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1012203</t>
+          <t>1010797</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>24155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>32590</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60033</t>
+          <t>60861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21731</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>44407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60916</t>
+          <t>60806</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>98015</t>
+          <t>99155</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>211207</t>
+          <t>213966</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>258744</t>
+          <t>259335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236166</t>
+          <t>237993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>282725</t>
+          <t>282610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>466014</t>
+          <t>464647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>528903</t>
+          <t>529283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165169</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210631</t>
+          <t>207969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134349</t>
+          <t>134487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176507</t>
+          <t>175356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308724</t>
+          <t>309665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>372240</t>
+          <t>372013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116031</t>
+          <t>116124</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163832</t>
+          <t>162378</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>35979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138334</t>
+          <t>137738</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190911</t>
+          <t>188416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>422698</t>
+          <t>418131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>504574</t>
+          <t>503848</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293677</t>
+          <t>293844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>367848</t>
+          <t>365787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>731475</t>
+          <t>735133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>842050</t>
+          <t>844338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1662576</t>
+          <t>1655264</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1776624</t>
+          <t>1781882</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2081440</t>
+          <t>2081381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2204343</t>
+          <t>2200253</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3775298</t>
+          <t>3776278</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3949811</t>
+          <t>3948067</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1021059</t>
+          <t>1021096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1129487</t>
+          <t>1135307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>978335</t>
+          <t>978396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1089717</t>
+          <t>1094348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2033737</t>
+          <t>2027120</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2188898</t>
+          <t>2184711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59533</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92874</t>
+          <t>91837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32516</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>58187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99684</t>
+          <t>98808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141925</t>
+          <t>142622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>297911</t>
+          <t>298810</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>350120</t>
+          <t>351760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>486584</t>
+          <t>487192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>553531</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>803018</t>
+          <t>803376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>884350</t>
+          <t>888906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311842</t>
+          <t>310662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367815</t>
+          <t>364322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>388818</t>
+          <t>387194</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>451081</t>
+          <t>454043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>720959</t>
+          <t>716682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>807720</t>
+          <t>801643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55459</t>
+          <t>56114</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88410</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20662</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>65601</t>
+          <t>65520</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103217</t>
+          <t>102115</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239093</t>
+          <t>240570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>301238</t>
+          <t>300487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151739</t>
+          <t>151399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201868</t>
+          <t>199427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>408165</t>
+          <t>405674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487333</t>
+          <t>488674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1031363</t>
+          <t>1028790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1122873</t>
+          <t>1121887</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1256452</t>
+          <t>1260523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1340831</t>
+          <t>1344138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2316805</t>
+          <t>2315837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2439168</t>
+          <t>2443856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>598069</t>
+          <t>600119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>687374</t>
+          <t>684803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>457877</t>
+          <t>454020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533953</t>
+          <t>533133</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078288</t>
+          <t>1075976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1194728</t>
+          <t>1193821</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54606</t>
+          <t>55886</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>32405</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67317</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>104691</t>
+          <t>104955</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>216438</t>
+          <t>218442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>262708</t>
+          <t>267471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289473</t>
+          <t>290390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335121</t>
+          <t>336119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>520713</t>
+          <t>521538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>590491</t>
+          <t>590607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>228124</t>
+          <t>228151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273666</t>
+          <t>276695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165162</t>
+          <t>165845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209054</t>
+          <t>211775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398880</t>
+          <t>402770</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>469939</t>
+          <t>471392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73470</t>
+          <t>73214</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111710</t>
+          <t>112780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88581</t>
+          <t>88281</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>129150</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353896</t>
+          <t>352087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>429018</t>
+          <t>428787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231540</t>
+          <t>233882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>294814</t>
+          <t>297131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>600220</t>
+          <t>604284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>701767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1583415</t>
+          <t>1582476</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1699856</t>
+          <t>1700393</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2075319</t>
+          <t>2070367</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2192314</t>
+          <t>2190737</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3691867</t>
+          <t>3694382</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3854357</t>
+          <t>3858434</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1171832</t>
+          <t>1179389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1287794</t>
+          <t>1289937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1044424</t>
+          <t>1045403</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1158941</t>
+          <t>1156805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2256395</t>
+          <t>2247966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2417426</t>
+          <t>2407715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>44049</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42472</t>
+          <t>61495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34308</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46979</t>
+          <t>67916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93529</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77195</t>
+          <t>96133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109555</t>
+          <t>134053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72351</t>
+          <t>79431</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>68227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85591</t>
+          <t>95102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>165880</t>
+          <t>193326</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145587</t>
+          <t>171562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186479</t>
+          <t>217723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169526</t>
+          <t>182127</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149395</t>
+          <t>162039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>190149</t>
+          <t>205971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>301910</t>
+          <t>329983</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>281625</t>
+          <t>308515</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>323552</t>
+          <t>351042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>471436</t>
+          <t>512111</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444004</t>
+          <t>481462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>503488</t>
+          <t>541404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>218915</t>
+          <t>234838</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200032</t>
+          <t>213497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>242462</t>
+          <t>256417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>368779</t>
+          <t>400457</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>347486</t>
+          <t>377793</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>390276</t>
+          <t>421093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>587693</t>
+          <t>635296</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>557793</t>
+          <t>604856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>617764</t>
+          <t>666835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511885</t>
+          <t>574910</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>511885</t>
+          <t>574910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511885</t>
+          <t>574910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>747433</t>
+          <t>815028</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>747433</t>
+          <t>815028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>747433</t>
+          <t>815028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1259318</t>
+          <t>1389938</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1259318</t>
+          <t>1389938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1259318</t>
+          <t>1389938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>176180</t>
+          <t>196669</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123289</t>
+          <t>168543</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>212849</t>
+          <t>229191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55429</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38625</t>
+          <t>48251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70586</t>
+          <t>76978</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>231609</t>
+          <t>258408</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>180039</t>
+          <t>224234</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>269582</t>
+          <t>291561</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>704623</t>
+          <t>527552</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>499578</t>
+          <t>481341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1163902</t>
+          <t>572956</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>463008</t>
+          <t>443657</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>356435</t>
+          <t>409209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>623197</t>
+          <t>477647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1167631</t>
+          <t>971208</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>919955</t>
+          <t>912219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1696359</t>
+          <t>1034303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>761740</t>
+          <t>830797</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540593</t>
+          <t>783692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>876710</t>
+          <t>889483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1211994</t>
+          <t>1093960</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1075325</t>
+          <t>1050590</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1474381</t>
+          <t>1139252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1973734</t>
+          <t>1924757</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1703639</t>
+          <t>1850743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2264375</t>
+          <t>1996381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>624662</t>
+          <t>653828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>446589</t>
+          <t>606075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>724252</t>
+          <t>706822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>500369</t>
+          <t>560355</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>365818</t>
+          <t>523193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>578213</t>
+          <t>599988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1125031</t>
+          <t>1214183</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>874792</t>
+          <t>1152623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1249500</t>
+          <t>1282394</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2267205</t>
+          <t>2208846</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2267205</t>
+          <t>2208846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2267205</t>
+          <t>2208846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2230799</t>
+          <t>2159711</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2230799</t>
+          <t>2159711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2230799</t>
+          <t>2159711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4498004</t>
+          <t>4368556</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4498004</t>
+          <t>4368556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4498004</t>
+          <t>4368556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,67 +9387,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11278</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5747</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19950</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10348</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5916</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>18197</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>25139</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80805</t>
+          <t>88561</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63345</t>
+          <t>70387</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110751</t>
+          <t>111159</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83952</t>
+          <t>95941</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69426</t>
+          <t>80153</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99975</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>164757</t>
+          <t>184502</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>143166</t>
+          <t>159225</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>200024</t>
+          <t>209975</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>225764</t>
+          <t>251980</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198634</t>
+          <t>222521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>250867</t>
+          <t>279346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>276182</t>
+          <t>308067</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254287</t>
+          <t>285309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298958</t>
+          <t>334153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>501946</t>
+          <t>560048</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>467510</t>
+          <t>523747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>538438</t>
+          <t>595880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>324626</t>
+          <t>351445</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>295894</t>
+          <t>320851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353673</t>
+          <t>379342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>287636</t>
+          <t>317075</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264287</t>
+          <t>294295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>311948</t>
+          <t>341225</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>612262</t>
+          <t>668520</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>574526</t>
+          <t>632168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>648905</t>
+          <t>706128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>641078</t>
+          <t>705847</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>641078</t>
+          <t>705847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>641078</t>
+          <t>705847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>658117</t>
+          <t>732361</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>658117</t>
+          <t>732361</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>658117</t>
+          <t>732361</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1299195</t>
+          <t>1438208</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1299195</t>
+          <t>1438208</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1299195</t>
+          <t>1438208</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>215978</t>
+          <t>254579</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162600</t>
+          <t>224133</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>247973</t>
+          <t>291359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70169</t>
+          <t>78173</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53779</t>
+          <t>63421</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85767</t>
+          <t>96384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>286147</t>
+          <t>332752</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>245221</t>
+          <t>295516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>328426</t>
+          <t>375402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>878957</t>
+          <t>730008</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>664397</t>
+          <t>676372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1463525</t>
+          <t>783619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>619311</t>
+          <t>619028</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>521282</t>
+          <t>579738</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>806384</t>
+          <t>661225</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1498268</t>
+          <t>1349037</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1252773</t>
+          <t>1285671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2203069</t>
+          <t>1422275</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1157030</t>
+          <t>1264905</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>888362</t>
+          <t>1202992</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1274333</t>
+          <t>1331174</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1790086</t>
+          <t>1732011</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1645391</t>
+          <t>1673130</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2112852</t>
+          <t>1785380</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2947116</t>
+          <t>2996916</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2645421</t>
+          <t>2906853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3333412</t>
+          <t>3073781</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1168203</t>
+          <t>1240111</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>891118</t>
+          <t>1174438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1280067</t>
+          <t>1300632</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1156783</t>
+          <t>1277888</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>953541</t>
+          <t>1225177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1254395</t>
+          <t>1334683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2324986</t>
+          <t>2517999</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2017138</t>
+          <t>2436905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2480498</t>
+          <t>2598295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3420168</t>
+          <t>3489603</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3420168</t>
+          <t>3489603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3420168</t>
+          <t>3489603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3636350</t>
+          <t>3707100</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3636350</t>
+          <t>3707100</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3636350</t>
+          <t>3707100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7056517</t>
+          <t>7196703</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7056517</t>
+          <t>7196703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7056517</t>
+          <t>7196703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
